--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2023_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:53</t>
+    <t xml:space="preserve">2026-09-24 01:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -567,13 +567,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +590,13 @@
         <v>30</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="4">
@@ -616,7 +616,7 @@
         <v>-0.33</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.34</v>
@@ -636,13 +636,13 @@
         <v>30</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="6">
@@ -659,13 +659,13 @@
         <v>30</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="7">
@@ -935,10 +935,10 @@
         <v>30</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.03</v>
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="22">
@@ -1021,19 +1021,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.37</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="23">
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.08</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2023_los_lagos.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:42</t>
+    <t xml:space="preserve">2026-10-01 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2023_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:14</t>
+    <t xml:space="preserve">2026-10-05 20:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
